--- a/.build-docs/context/Blueprint of Custom Excel Formats/GST_Refund_Stmt1A_Template.xlsx
+++ b/.build-docs/context/Blueprint of Custom Excel Formats/GST_Refund_Stmt1A_Template.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,31 @@
       <name val="Consolas"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -107,8 +130,38 @@
         <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -130,41 +183,80 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,26 +619,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000070C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C20"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="19.1640625" customWidth="1" min="2" max="2"/>
+    <col width="90.83203125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="1" ht="8.75" customHeight="1"/>
+    <row r="2" ht="28.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refund Statement 1A Template</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="10.25" customHeight="1">
+      <c r="B4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Refund Type</t>
@@ -558,7 +654,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Legal Basis</t>
@@ -570,7 +666,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Refund Code / Version</t>
@@ -582,7 +678,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="8"/>
+    <row r="9" ht="28.5" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Sheet Name</t>
@@ -594,191 +691,196 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>GSTIN and Return Period details</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="32" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Inward</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Details of inward supplies received and ITC claimed</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="17.25" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Outward</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Details of outward supplies issued at inverted rate</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="17.25" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Help</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Field specifications, validation rules, and usage guidance</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="14" ht="17.25" customHeight="1"/>
+    <row r="15" ht="20.5" customHeight="1">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Colour Coding</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Mandatory Columns</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Optional Columns</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Conditional Columns</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="19" ht="15" customHeight="1"/>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Refund template for ITC accumulated due to Inverted Tax Structure</t>
         </is>
       </c>
     </row>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000070C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>GSTIN</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr"/>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr"/>
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>15-character GSTIN of the refund applicant</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>From Period (MM-YYYY)</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr"/>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr"/>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Starting return period e.g., 07-2024 for July 2024</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>To Period (MM-YYYY)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr"/>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr"/>
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Ending return period e.g., 09-2024 for September 2024</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0000B050"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" style="13" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" style="13" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -787,8 +889,8 @@
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Inward Supply Type</t>
         </is>
@@ -798,17 +900,17 @@
           <t>Supplier GSTIN</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Doc Type</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Doc No</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Doc Date</t>
         </is>
@@ -818,7 +920,7 @@
           <t>Port Code</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
@@ -840,40 +942,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Inward Supply from Registered Person</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>24AABCT1332L1ZX</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Invoice/Bill of Entry</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>INV/2024/001</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>15-08-2024</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="n">
+      <c r="F2" s="12" t="inlineStr"/>
+      <c r="G2" s="11" t="n">
         <v>500000</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="11" t="n">
         <v>90000</v>
       </c>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr"/>
+      <c r="J2" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -881,26 +983,26 @@
       <formula1>"Import of Goods/Supplies from SEZ to DTA,Import of Services/Supplies from SEZ to DTA,Inward supplies liable to reverse charge,Inward Supply from Registered Person,Inward Supplies from ISD"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C10001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Invoice,Debit Note,Credit Note"</formula1>
+      <formula1>"Invoice/Bill of Entry,Debit Note,Credit Note"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E67E22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="13" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -908,13 +1010,13 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Outward Supply Type</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Doc Type</t>
         </is>
@@ -929,7 +1031,7 @@
           <t>Doc Date</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
@@ -951,34 +1053,34 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Invoice/Bill of Entry</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>SALE/2024/101</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>20-08-2024</t>
         </is>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="11" t="n">
         <v>200000</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="G2" s="9" t="inlineStr"/>
-      <c r="H2" s="9" t="inlineStr"/>
+      <c r="G2" s="12" t="inlineStr"/>
+      <c r="H2" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -986,212 +1088,215 @@
       <formula1>"B2B,B2C-Large,B2C-Small"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B10001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Invoice,Debit Note,Credit Note"</formula1>
+      <formula1>"Invoice/Bill of Entry,Debit Note,Credit Note"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E57"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="75" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="21.1640625" customWidth="1" min="2" max="2"/>
+    <col width="12.6640625" customWidth="1" min="3" max="3"/>
+    <col width="53.1640625" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="58.5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="19" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>1. Sheet Name: Header</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>The following table specifies the header fields for the refund application.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Field Category</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Field Type</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>GSTIN</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Text (15)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>15-character GSTIN of the refund applicant.</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>GSTIN regex; auto upper-cased and trimmed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>From Period</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Text (MM-YYYY)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Starting return period.
 Example: 07-2024 for July 2024</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Must be &gt;= 07-2017; &lt;= current; &lt;= To Period</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>To Period</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Text (MM-YYYY)</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Ending return period.
 Example: 09-2024 for September 2024</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Must be &gt;= 07-2017; &lt;= current; &gt;= From Period</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="8"/>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>2. Sheet Name: Inward</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>The following table specifies the fields for inward supply documents and ITC claimed.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Field Category</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Field Type</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Inward Supply Type</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Type of inward supply.
 Valid values:
@@ -1202,29 +1307,29 @@
   Inward Supplies from ISD</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Dropdown provided</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Supplier GSTIN</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Text (15)</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>GSTIN of supplier or ISD.
 Required for: Registered Person, ISD.
@@ -1232,171 +1337,172 @@
 Must differ from applicant GSTIN.</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>GSTIN regex; must differ from self</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Doc Type</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Type of document.
-Valid values: Invoice, Debit Note, Credit Note</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+Valid values: Invoice/Bill of Entry, Debit Note, Credit Note
+For Import of Goods, only Invoice/Bill of Entry is allowed.</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Dropdown provided</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Doc No</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Text (16)</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Document number or Bill of Entry number.
 Max 16 alphanumeric characters, / and - allowed.</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Cannot be 0 or special chars only</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Doc Date</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Text (DD-MM-YYYY)</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Date of document.
 Must be on or after 01-07-2017.
 Cannot be a future date.</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Valid calendar date; &lt;= To Period</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Port Code</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Text (6)</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Port code.
 Required ONLY for: Import of Goods/Supplies from SEZ to DTA.
 Leave blank for all other inward types.</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Exactly 6 alphanumeric characters</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Taxable value of the inward supply.
 Max 15 digits before decimal, 2 after.</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Must be &gt;= 0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>IGST</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Integrated Tax amount.
 Import types: IGST only (CGST/SGST must be blank).
@@ -1404,29 +1510,29 @@
 ISD: all three allowed simultaneously.</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Non-negative; mutual exclusivity per type</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>CGST</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Central Tax amount.
 Not applicable for Import types.
@@ -1434,241 +1540,242 @@
 For ISD: allowed alongside IGST.</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Non-negative; paired with SGST</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>SGST</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>State/UT Tax amount.
 Same rules as CGST.
 If CGST is provided, SGST must also be provided and vice versa.</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>Non-negative; paired with CGST</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="22"/>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>3. Sheet Name: Outward</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>The following table specifies the fields for outward supply documents at inverted rate.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Field Category</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Field Type</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Outward Supply Type</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Type of outward supply.
 Valid values: B2B, B2C-Large, B2C-Small</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Dropdown provided</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Doc Type</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Type of document.
-Valid values: Invoice, Debit Note, Credit Note</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
+Valid values: Invoice/Bill of Entry, Debit Note, Credit Note</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>Dropdown provided</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Doc No</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Text (16)</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Document number.
 For B2C-Small: leave blank. App auto-fills 'B2COTH' in JSON.
 For B2B and B2C-Large: mandatory.</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Max 16 alphanumeric + / and -</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Doc Date</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Text (DD-MM-YYYY)</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Date of document.
 For B2C-Small: leave blank. App auto-fills '01-07-2017' in JSON.
 For B2B and B2C-Large: mandatory.</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Valid calendar date; cannot be future</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Taxable value of the outward supply.
 Max 15 digits before decimal, 2 after.</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Must be &gt;= 0</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>IGST</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Integrated Tax amount.
 B2B: IGST alone OR CGST+SGST (not both).
@@ -1676,29 +1783,29 @@
 B2C-Small: not applicable (leave blank).</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Non-negative; &lt;= Taxable Value</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>CGST</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Central Tax amount.
 B2B: required if no IGST.
@@ -1706,161 +1813,167 @@
 B2C-Small: mandatory (with SGST).</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Non-negative; paired with SGST</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>SGST</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Number (15,2)</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>State/UT Tax amount.
 Same rules as CGST. Always paired with CGST.</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Non-negative; paired with CGST</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="34"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>4. Tax Mutual Exclusivity Rules</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="36"/>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>• INWARD — Import of Goods / Import of Services:  IGST only. CGST and SGST must be blank.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>• INWARD — RCM / Registered Person:  Either IGST alone OR (CGST + SGST) together. Cannot fill all three.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>• INWARD — ISD:  IGST, CGST, and SGST are all allowed simultaneously.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>• OUTWARD — B2B:  Either IGST alone OR (CGST + SGST) together. Cannot fill all three.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>• OUTWARD — B2C-Large:  IGST only. CGST and SGST must be blank.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>• OUTWARD — B2C-Small:  CGST + SGST only. IGST must be blank. Doc No and Date auto-filled by app.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>• ALL:  Sum of tax (IGST or CGST+SGST) must be &lt;= Taxable Value.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="44"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>5. Duplicate Detection</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+    <row r="46"/>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>• INWARD:  Duplicate key = Supplier GSTIN + Doc No + Financial Year + Month.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>• OUTWARD:  Duplicate key = Outward Type + Doc Type + Doc No + Financial Year + Month. DN/CN grouped as 'NOTE'.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>• Financial year adjustment: If invoice month is Jan-Mar (1-3), FY year is decremented by 1.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>• B2C-Small rows are excluded from duplicate checking (they share the auto-filled 'B2COTH' doc no).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="51"/>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>6. Running the Tool</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="53"/>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  python main.py                         → Opens file picker</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  python main.py input.xlsx              → Process specific file</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  python main.py input.xlsx --pretty     → Pretty-print JSON output</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  python main.py input.xlsx -v           → Verbose validation output</t>
         </is>
@@ -1893,6 +2006,7 @@
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>